--- a/forms/trg/Formulir_TRG_llgr-rg.xlsx
+++ b/forms/trg/Formulir_TRG_llgr-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Muhammad Ihsan Andi Dagong</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Faculty of Animal Science, Hasanuddin University</t>
@@ -963,7 +967,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1012,7 +1016,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1061,7 +1065,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1139,7 +1143,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1184,7 +1188,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1266,7 +1270,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1491,7 +1495,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1589,7 +1593,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1634,7 +1638,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1683,7 +1687,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1757,7 +1761,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
